--- a/data/trans_orig/IP31KM08_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM08_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53891</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44481</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>63591</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>52,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44857</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36718</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>54551</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>63493</t>
+          <t>43686</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52927</t>
+          <t>35506</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76379</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>108350</t>
+          <t>97577</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93608</t>
+          <t>84953</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123072</t>
+          <t>111428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>50,29%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67318</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57618</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76728</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>55,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>47,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>63,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>56852</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47158</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64991</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>55,9%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,37%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>63,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71683</t>
+          <t>56663</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82249</t>
+          <t>64843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>128536</t>
+          <t>123981</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113814</t>
+          <t>110130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143278</t>
+          <t>136605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>48193</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40224</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56577</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>53,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>62,95%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>38756</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30837</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>46688</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>41,5%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>33,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49166</t>
+          <t>40717</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39864</t>
+          <t>32483</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57229</t>
+          <t>48911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>87923</t>
+          <t>88910</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75160</t>
+          <t>77193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99215</t>
+          <t>100810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41687</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33303</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>49656</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>46,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>37,05%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>54636</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46704</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>62555</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>58,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>66,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44542</t>
+          <t>54693</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36479</t>
+          <t>46499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>62927</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>99178</t>
+          <t>96380</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87886</t>
+          <t>84480</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111941</t>
+          <t>108097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29417</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22350</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35604</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28041</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>21344</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33700</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>55,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>67,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23399</t>
+          <t>23653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>36591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>58742</t>
+          <t>59919</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49174</t>
+          <t>50942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68787</t>
+          <t>68891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26427</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20240</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33494</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>22048</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16389</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28745</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>44,02%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>57,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31633</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23943</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>53680</t>
+          <t>47935</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43635</t>
+          <t>38963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63248</t>
+          <t>56912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>84106</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>70400</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>97517</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>42,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>68414</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>46484</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>85237</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>31,74%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87016</t>
+          <t>64606</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73011</t>
+          <t>53511</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101256</t>
+          <t>75512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>155430</t>
+          <t>148712</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124494</t>
+          <t>132083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177260</t>
+          <t>166675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>113207</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>99796</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>126913</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>50,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>147123</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>130300</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>169053</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>68,26%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>125642</t>
+          <t>112034</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111402</t>
+          <t>101128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139647</t>
+          <t>123129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>272766</t>
+          <t>225241</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>250936</t>
+          <t>207278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303702</t>
+          <t>241870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>64,68%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,107 +2092,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>61305</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>47268</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>72223</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>42,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>62944</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>53204</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>72077</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>66426</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>57470</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>74909</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>57,53%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>49,77%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>64,88%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>127731</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>109878</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>142247</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>48,93%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>42,09%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>54,49%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>64710</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>49027</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>77149</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>40,58%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>30,75%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>48,38%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>106338</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>143720</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>46,42%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>38,67%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>84281</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>73363</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>98318</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>57,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>50,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>52565</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>43432</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>62305</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>40557</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>57996</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>42,47%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>50,23%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>133321</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>118805</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>151174</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>51,07%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>45,51%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>94751</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>82312</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>110434</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>59,42%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>51,62%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>69,25%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>147316</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>131250</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>168632</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>53,58%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>47,73%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>57,91%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>31167</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>23517</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>38409</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>47,32%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>35,71%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>37029</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>29422</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>43757</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>53,75%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>42,71%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>63,51%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32224</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24546</t>
+          <t>31107</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39783</t>
+          <t>46027</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>69252</t>
+          <t>70032</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58380</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79709</t>
+          <t>80436</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>34696</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>27454</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>42346</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>52,68%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>41,68%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>64,29%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>31866</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>25138</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>39473</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>46,25%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>36,49%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>57,29%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36807</t>
+          <t>31492</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>24329</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44485</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>68673</t>
+          <t>66188</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58216</t>
+          <t>55784</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79545</t>
+          <t>76720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>308079</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>283971</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>329881</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>45,59%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>42,03%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>48,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>403</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>280041</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>238736</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>305898</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>43,41%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>37,01%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>47,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>327310</t>
+          <t>284802</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>298254</t>
+          <t>264178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>353363</t>
+          <t>305471</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>607352</t>
+          <t>592881</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>561957</t>
+          <t>558430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>647430</t>
+          <t>625848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>367616</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>345814</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>391724</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>54,41%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>51,18%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>57,97%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>365090</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>339233</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>406395</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>56,59%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>52,58%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>62,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>405058</t>
+          <t>325430</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>379005</t>
+          <t>304761</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>434114</t>
+          <t>346054</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>770147</t>
+          <t>693046</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>730069</t>
+          <t>660079</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>815542</t>
+          <t>727497</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
